--- a/data_extactor/batch_10_fa/batch_0016_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0016_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Surveyors (نقشه‌برداران)</t>
+          <t>نقشه‌برداران (Surveyors)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>City Surveyor | County Surveyor | Land Surveyor | Licensed Land Surveyor | Mine Surveyor | Professional Land Surveyor | Registered Land Surveyor | Staff Land Surveyor | State Surveyor | Surveyor</t>
+          <t>نقشه‌بردار شهرداری | نقشه‌بردار شهرستان | نقشه‌بردار زمین | نقشه‌بردار زمین دارای پروانه | نقشه‌بردار معدن | نقشه‌بردار حرفه‌ای زمین | نقشه‌بردار ثبت‌شده زمین | نقشه‌بردار زمین کادر فنی | نقشه‌بردار ایالتی | نقشه‌بردار</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk AutoCAD Land Desktop | Bentley GeoPak Bridge | Bentley MicroStation | Bentley Systems InRoads Suite | CE SURVEYOR III | CMT Incorporated CogoCAD | Cadcorp desktop GIS | Carlson SurvCADD | Carlson SurvCE | Carlson Survey | CloudWorks | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Crones &amp; Associations Project Tracker Pro | Cyclone | نرم‌افزار ثبت داده | نرم‌افزار انتقال داده | نرم‌افزار نقشه‌کشی | ESRI ArcGIS software | ESRI ArcView | Geocomp Systems GeoNav | نرم‌افزار ژئودتیک | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی مکانیک خاک GDA | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | HYPACK HYSWEEP | HYPACK MAX | Latitude software | MicroSurvey FieldGenius | MicroSurveyCAD | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | NOAA Shoreline Data Explorer | PC-Mapper software | نرم‌افزار تحلیل و برآورد هزینه پروژه | نرم‌افزار یکپارچه‌سازی داده‌های پروژه | Sharetech Tabs Plus | Sokkia Imap | Sokkia Spectrum Survey Suite | نرم‌افزار مدل‌سازی سطح | نرم‌افزار نقشه‌برداری | نرم‌افزار پایگاه داده توپوگرافی | Trimble HYDROpro | Trimble Terramodel</t>
+          <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk AutoCAD Land Desktop | Bentley GeoPak Bridge | Bentley MicroStation | Bentley Systems InRoads Suite | CE SURVEYOR III | CMT Incorporated CogoCAD | Cadcorp desktop GIS | Carlson SurvCADD | Carlson SurvCE | Carlson Survey | CloudWorks | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Crones &amp; Associations Project Tracker Pro | Cyclone | نرم‌افزار ثبت داده‌ها | نرم‌افزار انتقال داده | نرم‌افزار نقشه‌کشی | نرم‌افزار ESRI ArcGIS | ESRI ArcView | Geocomp Systems GeoNav | نرم‌افزار ژئودتیک | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | HYPACK HYSWEEP | HYPACK MAX | Latitude software | MicroSurvey FieldGenius | MicroSurveyCAD | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | NOAA Shoreline Data Explorer | PC-Mapper software | نرم‌افزار تحلیل و برآورد هزینه پروژه | نرم‌افزار یکپارچه‌سازی داده‌های پروژه | Sharetech Tabs Plus | Sokkia Imap | Sokkia Spectrum Survey Suite | نرم‌افزار مدل‌سازی سطح | نرم‌افزار نظرسنجی | نرم‌افزار پایگاه داده توپوگرافی | Trimble HYDROpro | Trimble Terramodel</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | نوشتن | تفکر انتقادی | صحبت کردن | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>ریاضیات | درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | مهندسی و فناوری | جغرافیا | کامپیوتر و الکترونیک | طراحی | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مدیریت و اداره | زبان انگلیسی | قانون و دولت | آموزش و پرورش | اداری | پرسنل و منابع انسانی</t>
+          <t>ریاضیات | مهندسی و فناوری | جغرافیا | رایانه و الکترونیک | طراحی | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مدیریت و اداره | زبان انگلیسی | قانون و دولت | آموزش و پرورش | اداری | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک نوشتاری | استدلال قیاسی | استدلال ریاضی | دید نزدیک | بیان نوشتاری | استدلال استقرایی | توانایی کار با اعداد | درک شنیداری | بیان شفاهی | دید دور | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تجسم | جهت‌گیری فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت بستار | روانی ایده‌ها | درک عمق | دقت کنترل | مهارت انگشتان | ثبات دست و بازو</t>
+          <t>درک کتبی | استدلال قیاسی | استدلال ریاضی | بینایی نزدیک | بیان کتبی | استدلال استقرایی | توانایی عددی | درک شفاهی | بیان شفاهی | بینایی دور | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تجسم | جهت‌گیری فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت بستار | روانی ایده‌ها | درک عمق | دقت کنترل | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | تماس با دیگران | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تناوب تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نتایج کاری و خروجی‌های سایر کارکنان | سلامت و ایمنی سایر کارکنان | اهمیت تکرار کارهای مشابه | فضای بسته، با محیط کنترل‌شده | تعامل با مشتریان خارجی یا عموم مردم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامد خطا</t>
+          <t>ایمیل | اهمیت دقیق یا درست بودن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامد خطا</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Appraisers and Assessors of Real Estate | Architects, Except Landscape and Naval | Architectural and Civil Drafters | Cartographers and Photogrammetrists | Civil Engineering Technologists and Technicians | Civil Engineers | Conservation Scientists | Construction Managers | Construction and Building Inspectors | Cost Estimators | Forest and Conservation Technicians | Geodetic Surveyors | Geological Technicians, Except Hydrologic Technicians | Geoscientists, Except Hydrologists and Geographers | Government Property Inspectors and Investigators | Hydrologists | Landscape Architects | Mining and Geological Engineers, Including Mining Safety Engineers | Surveying and Mapping Technicians | Transportation Inspectors</t>
+          <t>ارزیابان و ممیزان املاک | معماران، به‌جز منظر و دریایی | نقشه‌کشان معماری و عمران | نقشه‌برداران و فتوگرامتریست‌ها | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | دانشمندان حفاظت | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | برآوردکنندگان هزینه | تکنسین‌های جنگل و حفاظت | نقشه‌برداران ژئودتیک | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | بازرسان و محققان اموال دولتی | آب‌شناسان | معماران منظر | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | تکنسین‌های نقشه‌برداری و نقشه‌کشی | بازرسان حمل‌ونقل</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geodetic Surveyors (نقشه‌برداران ژئودتیک)</t>
+          <t>نقشه‌برداران ژئودتیک (Geodetic Surveyors)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Geodesist | Geodetic Advisor | Geodetic Engineer | Geodetic Survey Director | Geodetic Surveyor | Land Surveyor | Licensed Land Surveyor</t>
+          <t>متخصص ژئودزی | مشاور ژئودزی | مهندس ژئودزی | مدیر ارشد نقشه‌برداری ژئودتیک | نقشه‌بردار ژئودتیک | نقشه‌بردار زمین | نقشه‌بردار زمین دارای پروانه</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Advanced Graphics Technology ProCogo | Amazon Web Services AWS software | Autodesk AutoCAD | Autodesk CAiCE Visual Transportation | Bentley MicroStation | C# | C++ | CMT CogoCAD | Carlson Civil Suite | Carlson Simplicity Sight Survey | ESRI ArcGIS software | ESRI ArcView | نرم‌افزار ایمیل | Geo-Plus | Geocomp Systems GeoCalc | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Hypertext markup language HTML | Linux | MicroSurvey Software MicroSurvey CAD | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | National Geodetic Survey NGS Geodetic Toolkit | National Geodetic Survey NGS VERTCON | نرم‌افزار برنامه‌نویسی شیءگرا | Oracle Java | QuickCogo | نرم‌افزار SAP | SiteComp Survey | Structured query language SQL | Traverse PC | Trimble Terramodel | Underhill Geomatics Copan | نرم‌افزار زبان مدل‌سازی واقعیت مجازی VRML | نرم‌افزار مرورگر وب</t>
+          <t>Advanced Graphics Technology ProCogo | نرم‌افزار Amazon Web Services AWS | Autodesk AutoCAD | Autodesk CAiCE Visual Transportation | Bentley MicroStation | C# | C++ | CMT CogoCAD | Carlson Civil Suite | Carlson Simplicity Sight Survey | نرم‌افزار ESRI ArcGIS | ESRI ArcView | نرم‌افزار ایمیل | Geo-Plus | Geocomp Systems GeoCalc | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | زبان نشانه‌گذاری ابرمتن HTML | Linux | MicroSurvey Software MicroSurvey CAD | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | National Geodetic Survey NGS Geodetic Toolkit | National Geodetic Survey NGS VERTCON | نرم‌افزار برنامه‌نویسی شیءگرا | Oracle Java | QuickCogo | نرم‌افزار SAP | SiteComp Survey | زبان پرس‌وجوی ساختاریافته SQL | Traverse PC | Trimble Terramodel | Underhill Geomatics Copan | نرم‌افزار زبان مدل‌سازی واقعیت مجازی VRML | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | تفکر انتقادی | گوش دادن فعال | نوشتن | صحبت کردن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
+          <t>ریاضیات | درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ریاضیات | مهندسی و فناوری | جغرافیا | کامپیوتر و الکترونیک | زبان انگلیسی | فیزیک | آموزش و پرورش | طراحی | خدمات مشتری و شخصی</t>
+          <t>ریاضیات | مهندسی و فناوری | جغرافیا | رایانه و الکترونیک | زبان انگلیسی | فیزیک | آموزش و پرورش | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال استقرایی | استدلال ریاضی | انعطاف‌پذیری بستار | نظم‌دهی اطلاعات | توانایی کار با اعداد | دید نزدیک | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | تجسم | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | دید دور | توجه انتخابی | سرعت ادراکی | سرعت بستار | حافظه‌سپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال ریاضی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | توانایی عددی | بینایی نزدیک | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | تجسم | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | بینایی دور | توجه انتخابی | سرعت ادراکی | سرعت بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | فضای بسته، با محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
+          <t>ایمیل | اهمیت دقیق یا درست بودن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Architectural and Civil Drafters | Atmospheric and Space Scientists | Calibration Technologists and Technicians | Cartographers and Photogrammetrists | Civil Engineering Technologists and Technicians | Civil Engineers | Data Scientists | Electrical and Electronic Engineering Technologists and Technicians | Geographers | Geographic Information Systems Technologists and Technicians | Geological Technicians, Except Hydrologic Technicians | Geoscientists, Except Hydrologists and Geographers | Hydrologic Technicians | Hydrologists | Remote Sensing Scientists and Technologists | Remote Sensing Technicians | Statistical Assistants | Surveying and Mapping Technicians | Surveyors | Traffic Technicians</t>
+          <t>نقشه‌کشان معماری و عمران | دانشمندان علوم جوی و فضایی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | نقشه‌برداران و فتوگرامتریست‌ها | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | دانشمندان داده | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | جغرافیدانان | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | تکنسین‌های هیدرولوژی | آب‌شناسان | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | دستیاران آماری | تکنسین‌های نقشه‌برداری و نقشه‌کشی | نقشه‌برداران | تکنسین‌های ترافیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aerospace Engineers (مهندسان هوافضا)</t>
+          <t>مهندسان هوافضا (Aerospace Engineers)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aeronautical Engineer | Aerospace Engineer | Aerospace Stress Engineer | Avionics Engineer | Design Engineer | Flight Controls Engineer | Flight Test Engineer | Structural Analysis Engineer | Systems Engineer | Test Engineer</t>
+          <t>مهندس هوانوردی | مهندس هوافضا | مهندس تنش هوافضا | مهندس آویونیک | مهندس طراحی | مهندس کنترل پرواز | مهندس آزمون پرواز | مهندس تحلیل سازه | مهندس سیستم‌ها | مهندس تست</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم | درک مطلب | نوشتن | صحبت کردن | ریاضیات | گوش دادن فعال | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | علوم | درک مطلب | نگارش | سخن گفتن | ریاضیات | گوش دادن فعال | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | طراحی | فیزیک | کامپیوتر و الکترونیک | زبان انگلیسی | مکانیک | تولید و پردازش</t>
+          <t>مهندسی و فناوری | ریاضیات | طراحی | فیزیک | رایانه و الکترونیک | زبان انگلیسی | مکانیک | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | بیان نوشتاری | استدلال ریاضی | درک شنیداری | بیان شفاهی | دید نزدیک | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توانایی کار با اعداد | اصالت | تجسم | دید دور | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | تشخیص رنگ بصری</t>
+          <t>درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال ریاضی | درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توانایی عددی | اصالت | تجسم | بینایی دور | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | فضای بسته، با محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aerospace Engineering and Operations Technologists and Technicians | Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Engineering Technicians | Automotive Engineers | Avionics Technicians | Calibration Technologists and Technicians | Electrical Engineers | Electrical and Electronic Engineering Technologists and Technicians | Electro-Mechanical and Mechatronics Technologists and Technicians | Electronics Engineers, Except Computer | Industrial Engineering Technologists and Technicians | Industrial Engineers | Manufacturing Engineers | Marine Engineers and Naval Architects | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Mechatronics Engineers | Robotics Engineers | Robotics Technicians</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | مهندسان خودرو | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | مهندسان دریایی و معماران کشتی | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,42 +664,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agricultural Engineers (مهندسان کشاورزی)</t>
+          <t>مهندسان کشاورزی (Agricultural Engineers)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Agricultural Engineer | Agricultural Systems Specialist | Conservation Engineer | Engineer | Field Engineer | Product Engineer | Product Technology Scientist | Project Engineer | Research Agricultural Engineer | Research Engineer</t>
+          <t>مهندس کشاورزی | کارشناس سامانه‌های کشاورزی | مهندس حفاظت منابع | مهندس | مهندس صحرایی | مهندس محصول | دانشمند فناوری محصول | مهندس پروژه | مهندس پژوهشی کشاورزی | مهندس تحقیق</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Dassault Systemes SolidWorks | ESRI ArcView | Eagle Point LANDCADD | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Word | Oracle Database | Oracle Java | PTC Creo Parametric | PTC Pro/Pipe | نرم‌افزار SAP | SAS | نرم‌افزار نظارت، کنترل و جمع‌آوری داده SCADA | نرم‌افزار مرورگر وب</t>
+          <t>Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Dassault Systemes SolidWorks | ESRI ArcView | Eagle Point LANDCADD | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Word | Oracle Database | Oracle Java | PTC Creo Parametric | PTC Pro/Pipe | نرم‌افزار SAP | SAS | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>صحبت کردن | نوشتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | علوم | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | علوم | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | کامپیوتر و الکترونیک | طراحی | فیزیک | ریاضیات | زیست‌شناسی | مکانیک | زبان انگلیسی | تولید مواد غذایی | شیمی | تولید و پردازش | ساختمان و ساخت‌وساز | جغرافیا | مدیریت و اداره | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | آموزش و پرورش</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | طراحی | فیزیک | ریاضیات | زیست‌شناسی | مکانیک | زبان انگلیسی | تولید مواد غذایی | شیمی | تولید و فرآوری | ساختمان و ساخت‌وساز | جغرافیا | مدیریت و اداره | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | درک شنیداری | درک نوشتاری | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | تجسم | دید نزدیک | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | استدلال ریاضی | اصالت | توانایی کار با اعداد | دید دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
+          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تجسم | بینایی نزدیک | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | استدلال ریاضی | اصالت | توانایی عددی | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | فضای بسته، با محیط کنترل‌شده | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | صرف زمان برای نشستن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | نامه‌ها و یادداشت‌های کتبی | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | صرف زمان برای نشستن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | نامه‌ها و یادداشت‌های کتبی | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Agricultural Sciences Teachers, Postsecondary | Agricultural Technicians | Biofuels Production Managers | Biofuels/Biodiesel Technology and Product Development Managers | Civil Engineers | Conservation Scientists | Environmental Engineering Technologists and Technicians | Environmental Engineers | Environmental Scientists and Specialists, Including Health | Farm Equipment Mechanics and Service Technicians | Farmers, Ranchers, and Other Agricultural Managers | Forest and Conservation Technicians | Geothermal Production Managers | Industrial Ecologists | Industrial Engineering Technologists and Technicians | Industrial Engineers | Precision Agriculture Technicians | Soil and Plant Scientists | Water Resource Specialists | Water/Wastewater Engineers</t>
+          <t>مدرسان علوم کشاورزی، پس از متوسطه | تکنسین‌های کشاورزی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مهندسان عمران | دانشمندان حفاظت | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | دانشمندان و متخصصان محیط زیست، شامل بهداشت | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | کشاورزان، دامداران و سایر مدیران کشاورزی | تکنسین‌های جنگل و حفاظت | مدیران تولید زمین‌گرمایی | بوم‌شناسان صنعتی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | تکنسین‌های کشاورزی دقیق | دانشمندان خاک و گیاه | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bioengineers and Biomedical Engineers (مهندسان زیستی و مهندسان زیست‌پزشکی)</t>
+          <t>مهندسان زیستی و مهندسان زیست‌پزشکی (Bioengineers and Biomedical Engineers)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biomedical Engineer | Biomedical Technician (Biomedical Tech) | Engineer | Process Engineer | Research Engineer</t>
+          <t>مهندس زیست‌پزشکی | تکنسین زیست‌پزشکی (Biomedical Tech) | مهندس | مهندس فرآیند | مهندس تحقیق</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADInstruments LabChart | نرم‌افزار شبیه‌سازی ANSYS | Ab Initio | Ada | Adobe Illustrator | Adobe Photoshop | زبان شبیه‌سازی کامپیوتری پیشرفته ACSL | ApE A Plasmid Editor | AspenTech HYSYS | Autodesk AutoCAD | نرم‌افزار مدل‌سازی بیومکانیکی | طراحی بیوراکتور | C | C++ | Cadence Allegro Design Entry Capture and Capture CIS | Cadence Encounter Test | محاسبه پارامترهای نگهداری بهینه COMPARE | نرم‌افزار کالیبراسیون | نرم‌افزار شبیه‌سازی مدار | نرم‌افزار ارزیابی خرابی‌های علت مشترک | نرم‌افزار دینامیک سیالات محاسباتی CFD | نرم‌افزار مدل‌سازی محاسباتی | نرم‌افزار تحلیل بحرانی | Dassault Systemes SolidWorks | نرم‌افزار ردیابی نقص | نرم‌افزار نمودارکشی | Dyadem FMEA Pro-6 | نرم‌افزار ERP | نرم‌افزار تحلیل تست الکترومکانیکی | نرم‌افزار تحلیل الکترومیوگراف | نرم‌افزار اتوماسیون طراحی الکترونیکی EDA | نرم‌افزار تست سیستم‌های تعبیه‌شده | نرم‌افزار تست انطباق تجهیزات | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار تحلیل حالات خرابی و اثرات آن FMEA | نرم‌افزار داده‌های نرخ خرابی FARADIP | نرم‌افزار پایگاه داده نرخ خرابی | نرم‌افزار مدل‌سازی خطا | نرم‌افزار تحلیل درخت خطا FTA | نرم‌افزار تحلیل المان محدود FEA | نرم‌افزار روش المان محدود FEM | نرم‌افزار پلتفرم نیرو | نرم‌افزار برنامه‌های حساس به نیرو FSA | نرم‌افزار مادون قرمز تبدیل فوریه FTIR | نرم‌افزار مدل‌سازی عملکردی | نرم‌افزار تحلیل راه رفتن | زبان توصیف سخت‌افزار HDL | برنامه شبیه‌سازی سلسله‌مراتبی با تأکید بر مدار مجتمع HSPICE | نرم‌افزار مدل‌سازی انسانی | زبان نشانه‌گذاری ابرمتن HTML | پیش‌پردازنده ابرمتن PHP | IBM Rational ClearCase | IBM Rational ClearQuest | IBM Rational RequisitePro | نرم‌افزار تحلیل تصویر | ImageJ | نرم‌افزار کنترل ابزار | نرم‌افزار اعتبارسنجی ابزار | نرم‌افزار محیط توسعه یکپارچه IDE | Intelligen SuperPro Designer | JavaScript | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Linux | Lucidchart | Maplesoft Maple | نرم‌افزار تست مواد | MathWorks Simulink | Mathsoft Mathcad | نرم‌افزار میانگین زمان بین خرابی‌ها MBTF | نرم‌افزار تصویربرداری پزشکی | نرم‌افزار اطلاعات پزشکی | نرم‌افزار Mentor Graphics | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Minitab | نرم‌افزار مدل‌سازی مولکولی | نرم‌افزار تحلیل حرکت | National Instruments LabVIEW | نرم‌افزار مدل‌سازی شبکه عصبی | NeuroSolutions for MatLab | نرم‌افزار تحلیل عددی | OrCAD Capture | Oracle Database | Oracle Java | PTC Creo Elements/Pro | PTC Pro/ENGINEER Wildfire | Polymath Software POLYMATH | نرم‌افزار نگهداری پیشگیرانه | نرم‌افزار برآورد پروژه | Python | R | نرم‌افزار توسعه سریع برنامه RAD | نرم‌افزار نمونه‌سازی سریع | Red Hat Enterprise Linux | نرم‌افزار نگهداری متمرکز بر قابلیت اطمینان RCM | نرم‌افزار مدیریت الزامات | نرم‌افزار تحلیل ریشه علت | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | SAS | SAS JMP | SNOINO RCM Pro | SNOINO Ttree | نرم‌افزار ورود طراحی شماتیک | برنامه شبیه‌سازی با تأکید بر مدار مجتمع SPICE | ابزارهای توسعه نرم‌افزار | Splunk Enterprise | نرم‌افزار مدل‌سازی تصادفی | Stratasys FDM MedModeler | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار تست سیستم | برنامه‌های تحلیل سیستم برای ارزیابی قابلیت اطمینان یکپارچه SAPHIRE | Technis BETAPLUS | نرم‌افزار تست خودکار | The MathWorks MATLAB | Thomson Reuters EndNote | نرم‌افزار ضبط حرکت سه‌بعدی | UNIX | زبان مدل‌سازی یکپارچه UML | نرم‌افزار طراحی رابط کاربری | Verilog | نرم‌افزار ابزار مجازی | Wolfram Research Mathematica | نرم‌افزار طراحی الکتریکی Zuken</t>
+          <t>ADInstruments LabChart | نرم‌افزار شبیه‌سازی ANSYS | Ab Initio | Ada | Adobe Illustrator | Adobe Photoshop | زبان شبیه‌سازی کامپیوتری پیشرفته ACSL | ApE A Plasmid Editor | AspenTech HYSYS | Autodesk AutoCAD | نرم‌افزار مدل‌سازی بیومکانیکی | طراحی بیوراکتور | C | C++ | Cadence Allegro Design Entry Capture and Capture CIS | Cadence Encounter Test | محاسبه پارامترهای نگهداری بهینه COMPARE | نرم‌افزار کالیبراسیون | نرم‌افزار شبیه‌سازی مدار | نرم‌افزار ارزیابی خرابی‌های علت مشترک | نرم‌افزار دینامیک سیالات محاسباتی CFD | نرم‌افزار مدل‌سازی محاسباتی | نرم‌افزار تحلیل بحرانی | Dassault Systemes SolidWorks | نرم‌افزار ردیابی نقص | نرم‌افزار نمودارکشی | Dyadem FMEA Pro-6 | نرم‌افزار ERP | نرم‌افزار تحلیل تست الکترومکانیکی | نرم‌افزار تحلیل الکترومیوگراف | نرم‌افزار اتوماسیون طراحی الکترونیکی EDA | نرم‌افزار تست سیستم‌های تعبیه‌شده | نرم‌افزار تست انطباق تجهیزات | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی و اثرات آن FMEA | نرم‌افزار داده‌های نرخ خرابی FARADIP | نرم‌افزار پایگاه داده نرخ خرابی | نرم‌افزار مدل‌سازی خطا | نرم‌افزار تحلیل درخت خطا FTA | نرم‌افزار تحلیل المان محدود FEA | نرم‌افزار روش المان محدود FEM | نرم‌افزار پلتفرم نیرو | نرم‌افزار برنامه‌های حساس به نیرو FSA | نرم‌افزار مادون قرمز تبدیل فوریه FTIR | نرم‌افزار مدل‌سازی عملکردی | نرم‌افزار تحلیل راه رفتن | زبان توصیف سخت‌افزار HDL | Hierarchical simulation program with integrated circuit emphasis HSPICE | نرم‌افزار مدل‌سازی انسانی | زبان نشانه‌گذاری ابرمتن HTML | Hypertext preprocessor PHP | IBM Rational ClearCase | IBM Rational ClearQuest | IBM Rational RequisitePro | نرم‌افزار تحلیل تصویر | ImageJ | نرم‌افزار کنترل ابزار | نرم‌افزار اعتبارسنجی ابزار | نرم‌افزار محیط توسعه یکپارچه IDE | Intelligen SuperPro Designer | JavaScript | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Linux | Lucidchart | Maplesoft Maple | نرم‌افزار تست مواد | MathWorks Simulink | Mathsoft Mathcad | نرم‌افزار میانگین زمان بین خرابی‌ها MBTF | نرم‌افزار تصویربرداری پزشکی | نرم‌افزار اطلاعات پزشکی | نرم‌افزار Mentor Graphics | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Minitab | نرم‌افزار شبیه‌سازی مولکولی | نرم‌افزار تحلیل حرکت | National Instruments LabVIEW | نرم‌افزار مدل‌سازی شبکه عصبی | NeuroSolutions for MatLab | نرم‌افزار تحلیل عددی | OrCAD Capture | Oracle Database | Oracle Java | PTC Creo Elements/Pro | PTC Pro/ENGINEER Wildfire | Polymath Software POLYMATH | نرم‌افزار نگهداری پیشگیرانه | نرم‌افزار برآورد پروژه | Python | R | نرم‌افزار توسعه سریع برنامه RAD | نرم‌افزار نمونه‌سازی سریع | Red Hat Enterprise Linux | نرم‌افزار نگهداری متمرکز بر قابلیت اطمینان RCM | نرم‌افزار مدیریت الزامات | نرم‌افزار تحلیل علت ریشه‌ای | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | SAS | SAS JMP | SNOINO RCM Pro | SNOINO Ttree | نرم‌افزار ورود طراحی شماتیک | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | ابزارهای توسعه نرم‌افزار | Splunk Enterprise | نرم‌افزار مدل‌سازی تصادفی | Stratasys FDM MedModeler | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار تست سیستم | برنامه‌های تحلیل سیستم برای ارزیابی قابلیت اطمینان یکپارچه SAPHIRE | Technis BETAPLUS | نرم‌افزار تست خودکار | The MathWorks MATLAB | Thomson Reuters EndNote | نرم‌افزار ضبط حرکت سه‌بعدی | UNIX | زبان مدل‌سازی یکپارچه UML | نرم‌افزار طراحی رابط کاربری | Verilog | نرم‌افزار ابزار مجازی | Wolfram Research Mathematica | نرم‌افزار طراحی الکتریکی Zuken</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>صحبت کردن | نوشتن | گوش دادن فعال | درک مطلب | علوم | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | علوم | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | کامپیوتر و الکترونیک | ریاضیات | فیزیک | طراحی | زیست‌شناسی | زبان انگلیسی | پزشکی و دندانپزشکی | آموزش و پرورش | شیمی | مدیریت و اداره</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | فیزیک | طراحی | زیست‌شناسی | زبان انگلیسی | پزشکی و دندان‌پزشکی | آموزش و پرورش | شیمی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | نظم‌دهی اطلاعات | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | اصالت | تشخیص گفتار | تجسم | انعطاف‌پذیری بستار | توانایی کار با اعداد | وضوح گفتار | توجه انتخابی | سرعت ادراکی</t>
+          <t>استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | اصالت | تشخیص گفتار | تجسم | انعطاف‌پذیری بستار | توانایی عددی | وضوح گفتار | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | فضای بسته، با محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | بحث‌های حضوری با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | مکالمات تلفنی | تماس با دیگران | سطح رقابت</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | مکالمات تلفنی | ارتباط با دیگران | سطح رقابت</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Biochemists and Biophysicists | Bioinformatics Scientists | Bioinformatics Technicians | Biological Technicians | Calibration Technologists and Technicians | Chemical Engineers | Chemists | Clinical Data Managers | Data Scientists | Geneticists | Industrial Engineering Technologists and Technicians | Materials Scientists | Mechanical Engineering Technologists and Technicians | Medical Equipment Repairers | Medical and Clinical Laboratory Technologists | Microbiologists | Molecular and Cellular Biologists | Nanosystems Engineers | Nanotechnology Engineering Technologists and Technicians | Natural Sciences Managers</t>
+          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | تکنسین‌های زیستی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان شیمی | شیمی‌دانان | مدیران داده‌های بالینی | دانشمندان داده | ژنتیک‌دان‌ها | تکنسین‌ها و کارشناسان مهندسی صنایع | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | تعمیرکاران تجهیزات پزشکی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مدیران علوم طبیعی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,42 +778,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chemical Engineers (مهندسان شیمی)</t>
+          <t>مهندسان شیمی (Chemical Engineers)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chemical Engineer | Development Engineer | Engineer | Engineering Scientist | Process Control Engineer | Process Engineer | Project Engineer | Refinery Process Engineer | Research Chemical Engineer | Scientist</t>
+          <t>مهندس شیمی | مهندس توسعه | مهندس | دانشمند مهندسی | مهندس کنترل فرایند | مهندس فرآیند | مهندس پروژه | مهندس فرایند پالایشگاه | مهندس پژوهشی شیمی | دانشمند</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار شبیه‌سازی فرآیند جذب | Applied Flow Technology AFT Arrow | Applied Flow Technology AFT Fathom | AspenTech aspenONE | Autodesk AutoCAD | C | C++ | CD-adapco STAR-CAD | Cerebro CerebroMix | ChemicaLogic SteamTab | Chempute Software ChemDraw | Chempute Software Engineer's Aide SINET | Chempute Software EstPro | Chempute Software SuperPro Designer | Chempute Software VisiMix | Chemstations CHEMCAD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Control Station ENGINEER | Dassault Systemes CATIA | Dassault Systemes SolidWorks | EPCON International CHEMPRO Engineering Suite | EPCON International SYSTEM 7 Process Explorer | EPCON International SiNET | G&amp;P Engineering Software EngVert | G&amp;P Engineering Software PhysProps | G&amp;P Engineering Software PipeDrop | GE Fanuc Proficy Machine Edition | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Madison Technical Software Chempak Plus | Madison Technical Software Enviropak | Madison Technical Software Steampak | Microsoft Access | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual C# .NET | Microsoft Word | Minitab | National Instruments LabVIEW | PTC Creo Parametric | Prode PD-Plus | R | نرم‌افزار پایگاه داده رابطه‌ای | نرم‌افزار SAP | SoftLab PHEdesign | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار نظارت، کنترل و جمع‌آوری داده SCADA | The MathWorks MATLAB | Thermal Analysis Systems The Energy Analyst</t>
+          <t>نرم‌افزار شبیه‌سازی فرآیند جذب | Applied Flow Technology AFT Arrow | Applied Flow Technology AFT Fathom | AspenTech aspenONE | Autodesk AutoCAD | C | C++ | CD-adapco STAR-CAD | Cerebro CerebroMix | ChemicaLogic SteamTab | Chempute Software ChemDraw | Chempute Software Engineer's Aide SINET | Chempute Software EstPro | Chempute Software SuperPro Designer | Chempute Software VisiMix | Chemstations CHEMCAD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Control Station ENGINEER | Dassault Systemes CATIA | Dassault Systemes SolidWorks | EPCON International CHEMPRO Engineering Suite | EPCON International SYSTEM 7 Process Explorer | EPCON International SiNET | G&amp;P Engineering Software EngVert | G&amp;P Engineering Software PhysProps | G&amp;P Engineering Software PipeDrop | GE Fanuc Proficy Machine Edition | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Madison Technical Software Chempak Plus | Madison Technical Software Enviropak | Madison Technical Software Steampak | Microsoft Access | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual C# .NET | Microsoft Word | Minitab | National Instruments LabVIEW | PTC Creo Parametric | Prode PD-Plus | R | نرم‌افزار پایگاه داده رابطه‌ای | نرم‌افزار SAP | SoftLab PHEdesign | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | The MathWorks MATLAB | Thermal Analysis Systems The Energy Analyst</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>علوم | تفکر انتقادی | درک مطلب | یادگیری فعال | ریاضیات | صحبت کردن | گوش دادن فعال | نوشتن | نظارت</t>
+          <t>علوم | تفکر انتقادی | درک مطلب | یادگیری فعال | ریاضیات | سخن گفتن | گوش دادن فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | شیمی | ریاضیات | طراحی | فیزیک | تولید و پردازش | زبان انگلیسی | کامپیوتر و الکترونیک | مکانیک</t>
+          <t>مهندسی و فناوری | شیمی | ریاضیات | طراحی | فیزیک | تولید و فرآوری | زبان انگلیسی | رایانه و الکترونیک | مکانیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | استدلال ریاضی | دید نزدیک | توانایی کار با اعداد | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار | بیان نوشتاری | تجسم | سرعت ادراکی | وضوح گفتار | تشخیص گفتار | دید دور | توجه انتخابی | سرعت بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | بینایی نزدیک | توانایی عددی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار | بیان کتبی | تجسم | سرعت ادراکی | وضوح گفتار | تشخیص گفتار | بینایی دور | توجه انتخابی | سرعت بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | فضای بسته، با محیط کنترل‌شده | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | تماس با دیگران | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | ارتباط با دیگران | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Biofuels Processing Technicians | Biofuels/Biodiesel Technology and Product Development Managers | Biomass Plant Technicians | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Chemical Technicians | Chemists | Fuel Cell Engineers | Industrial Engineering Technologists and Technicians | Industrial Engineers | Manufacturing Engineers | Materials Engineers | Materials Scientists | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Mechatronics Engineers | Nanosystems Engineers | Nanotechnology Engineering Technologists and Technicians | Nuclear Engineers | Petroleum Engineers</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | تکنسین‌های شیمی | شیمی‌دانان | مهندسان پیل سوختی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | مهندسان مواد | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مهندسان هسته‌ای | مهندسان نفت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,42 +835,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Civil Engineers (مهندسان عمران)</t>
+          <t>مهندسان عمران (Civil Engineers)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>City Engineer | Civil Engineer | County Engineer | Design Engineer | Engineer | Geotechnical Engineer | Licensed Engineer | Project Engineer | Railroad Design Consultant | Structural Engineer</t>
+          <t>مهندس شهرداری | مهندس عمران | مهندس شهرستان | مهندس طراحی | مهندس | مهندس ژئوتکنیک | مهندس دارای پروانه | مهندس پروژه | مشاور طراحی راه‌آهن | مهندس سازه</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Apache Subversion SVN | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Land Desktop | Autodesk Revit | Bentley GeoPak Bridge | Bentley Haestad Methods CivilStorm | Bentley InRoads Suite | Bentley MicroStation | Bentley STAAD | نرم‌افزار طراحی پل | C | نرم‌افزار نقشه‌کشی | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Corel WordPerfect Office Suite | نرم‌افزار برآورد هزینه | Dassault Systemes Abaqus | Dassault Systemes CATIA | Dassault Systemes SolidWorks | ESRI ArcGIS software | ESRI ArcInfo | ESRI ArcView | Eagle Point Site Design | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار تحلیل المان محدود FEA | Formula translation/translator FORTRAN | GT STRUDL | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | نرم‌افزار گرافیکی | HEC-1 | HEC-HMS | نرم‌افزار تحلیل هیدرولیکی | نرم‌افزار مدل‌سازی هیدرولیکی | HydroCAD Software Solutions HydroCAD Stormwater Modeling System | Intergraph MGE | MAYA Nastran | Mathsoft Mathcad | Microsoft Access | Microsoft ActiveX | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visual Basic | Microsoft Word | Minitab | National Instruments LabVIEW | Oracle Business Intelligence Enterprise Edition | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | Procore software | نرم‌افزار طراحی جاده | نرم‌افزار SAP | نرم‌افزار زمان‌بندی | Shell script | SmugMug Flickr | نرم‌افزار هیدرولوژی آب‌های سطحی | نرم‌افزار نظارت، کنترل و جمع‌آوری داده SCADA | The Gordian Group PROGEN Online | The MathWorks MATLAB | Trimble Geomatics Office | Trimble SketchUp Pro | Trimble Terramodel | Verilog | نرم‌افزار مرورگر وب | WinTR-55</t>
+          <t>Adobe Acrobat | Apache Subversion SVN | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Land Desktop | Autodesk Revit | Bentley GeoPak Bridge | Bentley Haestad Methods CivilStorm | Bentley InRoads Suite | Bentley MicroStation | Bentley STAAD | نرم‌افزار طراحی پل | C | نرم‌افزار نقشه‌کشی | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Corel WordPerfect Office Suite | نرم‌افزار برآورد هزینه | Dassault Systemes Abaqus | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | ESRI ArcView | Eagle Point Site Design | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار تحلیل المان محدود FEA | Formula translation/translator FORTRAN | GT STRUDL | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | نرم‌افزار گرافیکی | HEC-1 | HEC-HMS | نرم‌افزار تحلیل هیدرولیکی | نرم‌افزار مدل‌سازی هیدرولیکی | HydroCAD Software Solutions HydroCAD Stormwater Modeling System | Intergraph MGE | MAYA Nastran | Mathsoft Mathcad | Microsoft Access | Microsoft ActiveX | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visual Basic | Microsoft Word | Minitab | National Instruments LabVIEW | Oracle Business Intelligence Enterprise Edition | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | Procore software | نرم‌افزار طراحی جاده | نرم‌افزار SAP | نرم‌افزار زمان‌بندی | Shell script | SmugMug Flickr | نرم‌افزار هیدرولوژی آب‌های سطحی | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | The Gordian Group PROGEN Online | The MathWorks MATLAB | Trimble Geomatics Office | Trimble SketchUp Pro | Trimble Terramodel | Verilog | نرم‌افزار مرورگر وب | WinTR-55</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | صحبت کردن | ریاضیات | درک مطلب | علوم | نظارت | یادگیری فعال | نوشتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | ریاضیات | درک مطلب | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | ساختمان و ساخت‌وساز | ریاضیات | زبان انگلیسی | فیزیک | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | حمل و نقل</t>
+          <t>طراحی | مهندسی و فناوری | ساختمان و ساخت‌وساز | ریاضیات | زبان انگلیسی | فیزیک | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | ایمنی و امنیت عمومی | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | نظم‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی کار با اعداد | تجسم | روانی ایده‌ها | دید نزدیک | دید دور | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | سرعت ادراکی | اصالت | توجه انتخابی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | تجسم | روانی ایده‌ها | بینایی نزدیک | بینایی دور | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | سرعت ادراکی | اصالت | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | فضای بسته، با محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | تماس با دیگران | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | تناوب تصمیم‌گیری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | ارتباط با دیگران | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Architects, Except Landscape and Naval | Architectural and Civil Drafters | Architectural and Engineering Managers | Brownfield Redevelopment Specialists and Site Managers | Civil Engineering Technologists and Technicians | Construction Managers | Construction and Building Inspectors | Electrical Engineers | Environmental Engineers | Facilities Managers | First-Line Supervisors of Construction Trades and Extraction Workers | Industrial Engineers | Maintenance and Repair Workers, General | Marine Engineers and Naval Architects | Mechanical Engineering Technologists and Technicians | Mining and Geological Engineers, Including Mining Safety Engineers | Solar Energy Installation Managers | Transportation Engineers | Water/Wastewater Engineers | Wind Energy Engineers</t>
+          <t>معماران، به‌جز منظر و دریایی | نقشه‌کشان معماری و عمران | مدیران معماری و مهندسی | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | تکنسین‌ها و کارشناسان مهندسی عمران | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | مهندسان برق | مهندسان محیط زیست | مدیران تسهیلات | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | مهندسان صنایع | کارگران نگهداری و تعمیرات عمومی | مهندسان دریایی و معماران کشتی | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | مدیران نصب انرژی خورشیدی | مهندسان حمل و نقل | مهندسان آب و فاضلاب | مهندسان انرژی بادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Transportation Engineers (مهندسان حمل و نقل)</t>
+          <t>مهندسان حمل و نقل (Transportation Engineers)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Engineer | Project Engineer | Rail Engineer | Roadway Designer | Roadway Engineer | State Roadway Design Engineer | Traffic Engineer | Traffic Operations Engineer | Transportation Engineer</t>
+          <t>مهندس | مهندس پروژه | مهندس راه‌آهن | طراح راه | مهندس راه | مهندس طراحی راه‌های ایالتی | مهندس ترافیک | مهندس عملیات ترافیک | مهندس حمل‌ونقل</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Land Desktop | Bentley GEOPAK Civil Engineering Suite | Bentley InRoads Suite | Bentley MicroStation | Citilabs Cube | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Cubic Synchro Studio | ESRI ArcGIS software | McTrans Center TSIS-CORSIM | McTrans HCS+ | McTrans TRANSYT-7F | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | OpenRoads Designer | Oracle Primavera Enterprise Project Portfolio Management | PTV Vissim | Python | SIDRA INTERSECTION | زبان پرس‌وجوی ساختاریافته SQL | Trafficware SimTraffic | Trafficware SynchroGreen | Transoft Solutions AutoTURN | Visual Solutions VisSIM | سیستم مدیریت انبار WMS | نرم‌افزار مرورگر وب</t>
+          <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Land Desktop | Bentley GEOPAK Civil Engineering Suite | Bentley InRoads Suite | Bentley MicroStation | Citilabs Cube | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Cubic Synchro Studio | نرم‌افزار ESRI ArcGIS | McTrans Center TSIS-CORSIM | McTrans HCS+ | McTrans TRANSYT-7F | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | OpenRoads Designer | Oracle Primavera Enterprise Project Portfolio Management | PTV Vissim | Python | SIDRA INTERSECTION | زبان پرس‌وجوی ساختاریافته SQL | Trafficware SimTraffic | Trafficware SynchroGreen | Transoft Solutions AutoTURN | Visual Solutions VisSIM | سیستم مدیریت انبار WMS | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | صحبت کردن | نوشتن | درک مطلب | ریاضیات | گوش دادن فعال | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | ریاضیات | گوش دادن فعال | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | حمل و نقل | ساختمان و ساخت‌وساز | ریاضیات | زبان انگلیسی | فیزیک | مدیریت و اداره | خدمات مشتری و شخصی | کامپیوتر و الکترونیک | قانون و دولت | ایمنی و امنیت عمومی | آموزش و پرورش</t>
+          <t>مهندسی و فناوری | طراحی | حمل و نقل | ساختمان و ساخت‌وساز | ریاضیات | زبان انگلیسی | فیزیک | مدیریت و اداره | خدمات مشتری و شخصی | رایانه و الکترونیک | قانون و دولت | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال ریاضی | توانایی کار با اعداد | نظم‌دهی اطلاعات | تجسم | دید نزدیک | تشخیص گفتار | روانی ایده‌ها | وضوح گفتار | دید دور | اصالت | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی</t>
+          <t>استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال ریاضی | توانایی عددی | ترتیب‌دهی اطلاعات | تجسم | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | وضوح گفتار | بینایی دور | اصالت | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فضای بسته، با محیط کنترل‌شده | تماس با دیگران | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نتایج کاری و خروجی‌های سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | تناوب تصمیم‌گیری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aerospace Engineers | Architectural and Civil Drafters | Architectural and Engineering Managers | Automotive Engineers | Brownfield Redevelopment Specialists and Site Managers | Civil Engineering Technologists and Technicians | Civil Engineers | Construction Managers | Construction and Building Inspectors | Environmental Engineers | Highway Maintenance Workers | Industrial Engineers | Logistics Engineers | Mining and Geological Engineers, Including Mining Safety Engineers | Project Management Specialists | Solar Energy Installation Managers | Traffic Technicians | Transportation Planners | Transportation, Storage, and Distribution Managers | Water/Wastewater Engineers</t>
+          <t>مهندسان هوافضا | نقشه‌کشان معماری و عمران | مدیران معماری و مهندسی | مهندسان خودرو | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | مهندسان محیط زیست | کارگران نگهداری بزرگراه‌ها | مهندسان صنایع | مهندسان لجستیک | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | متخصصان مدیریت پروژه | مدیران نصب انرژی خورشیدی | تکنسین‌های ترافیک | برنامه‌ریزان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Water/Wastewater Engineers (مهندسان آب و فاضلاب)</t>
+          <t>مهندسان آب و فاضلاب (Water/Wastewater Engineers)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Consulting Engineer | County Engineer | Engineer | Project Development Engineer</t>
+          <t>مهندس مشاور | مهندس شهرستان | مهندس | مهندس توسعه پروژه</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bash | Bentley GEOPAK Civil Engineering Suite | Bentley InRoads Suite | Bentley MicroStation | Bentley SewerCAD | Bentley StormCAD | Bentley WaterCAD | برنامه‌های نرم‌افزاری تجاری | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | DHI MIKE URBAN | EPA Storm Water Management Model SWMM | ESRI ArcGIS software | نرم‌افزار ESRI | Eagle Point LANDCADD | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های اطلاعات جغرافیایی GIS | Google Chrome | HEC-1 | HEC-GeoRAS | HEC-HMS | HEC-RAS | نرم‌افزار مدل‌سازی هیدرولیکی | HydroCAD Software Solutions HydroCAD Stormwater Modeling System | KYPipe | MWH Soft InfoSWMM | MapInfo | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Minitab | Mozilla Firefox | NIWA Tideda | OpenRoads Designer | Oracle Java | Python | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار نظارت، کنترل و جمع‌آوری داده SCADA | Wallingford Software InfoSewer | Wallingford Software InfoWorks WS | نرم‌افزار مرورگر وب | XP Software XPSWMM</t>
+          <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bash | Bentley GEOPAK Civil Engineering Suite | Bentley InRoads Suite | Bentley MicroStation | Bentley SewerCAD | Bentley StormCAD | Bentley WaterCAD | برنامه‌های نرم‌افزاری تجاری | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | DHI MIKE URBAN | EPA Storm Water Management Model SWMM | نرم‌افزار ESRI ArcGIS | نرم‌افزار ESRI | Eagle Point LANDCADD | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Google Chrome | HEC-1 | HEC-GeoRAS | HEC-HMS | HEC-RAS | نرم‌افزار مدل‌سازی هیدرولیکی | HydroCAD Software Solutions HydroCAD Stormwater Modeling System | KYPipe | MWH Soft InfoSWMM | MapInfo | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Minitab | Mozilla Firefox | NIWA Tideda | OpenRoads Designer | Oracle Java | Python | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Wallingford Software InfoSewer | Wallingford Software InfoWorks WS | نرم‌افزار مرورگر وب | XP Software XPSWMM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نوشتن | درک مطلب | گوش دادن فعال | ریاضیات | صحبت کردن | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | نگارش | درک مطلب | گوش دادن فعال | ریاضیات | سخن گفتن | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | زبان انگلیسی | ریاضیات | ساختمان و ساخت‌وساز | مدیریت و اداره | مکانیک | فیزیک | شیمی | خدمات مشتری و شخصی | قانون و دولت | زیست‌شناسی | فروش و بازاریابی | کامپیوتر و الکترونیک | اقتصاد و حسابداری</t>
+          <t>مهندسی و فناوری | طراحی | زبان انگلیسی | ریاضیات | ساختمان و ساخت‌وساز | مدیریت و اداره | مکانیک | فیزیک | شیمی | خدمات مشتری و شخصی | قانون و دولت | زیست‌شناسی | فروش و بازاریابی | رایانه و الکترونیک | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال استقرایی | نظم‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی کار با اعداد | تجسم | دید نزدیک | اصالت | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | دید دور | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | تجسم | بینایی نزدیک | اصالت | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | بینایی دور | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فضای بسته، با محیط کنترل‌شده | تماس با دیگران | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | سطح رقابت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Brownfield Redevelopment Specialists and Site Managers | Chemical Engineers | Civil Engineers | Conservation Scientists | Energy Engineers, Except Wind and Solar | Environmental Engineering Technologists and Technicians | Environmental Engineers | Environmental Restoration Planners | Environmental Science and Protection Technicians, Including Health | Geothermal Production Managers | Hydroelectric Plant Technicians | Hydroelectric Production Managers | Hydrologic Technicians | Hydrologists | Industrial Ecologists | Petroleum Engineers | Transportation Engineers | Water Resource Specialists | Water and Wastewater Treatment Plant and System Operators | Wind Energy Engineers</t>
+          <t>متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مهندسان شیمی | مهندسان عمران | دانشمندان حفاظت | مهندسان انرژی، به جز باد و خورشید | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | مدیران تولید زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | مهندسان نفت | مهندسان حمل و نقل | متخصصان منابع آب | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | مهندسان انرژی بادی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,42 +1006,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Computer Hardware Engineers (مهندسان سخت‌افزار کامپیوتر)</t>
+          <t>مهندسان سخت‌افزار کامپیوتر (Computer Hardware Engineers)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design Engineer | Engineer | Field Service Engineer | Hardware Design Engineer | Hardware Engineer | Physical Design Engineer | Project Engineer | Staff Engineer | Systems Integration Engineer</t>
+          <t>مهندس طراحی | مهندس | مهندس خدمات صحرایی | مهندس طراحی سخت‌افزار | مهندس سخت‌افزار | مهندس طراحی فیزیکی | مهندس پروژه | مهندس کادر فنی | مهندس یکپارچه‌سازی سامانه‌ها</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ASSET JTAG ScanWorks | Apache Subversion SVN | نرم‌افزار سنتز منطق مدار مجتمع با کاربرد خاص ASIC | Autodesk AutoCAD | نرم‌افزار تولید برنامه تست خودکار ATPG | نرم‌افزار نمودار بلوکی | زبان توصیف اسکن مرزی BSDL | نرم‌افزار درج اسکن مرزی | نرم‌افزار دیباگ خودآزمایی داخلی BIST | C | C++ | Cadence Allegro PCB Designer | Cadence Concept | Cadence Dracula | Cadence Encounter RTL Compiler | Cadence Opus | نرم‌افزار Cadence OrCAD | Cadence PSpice | Cadence Schematic Composer | Cadence Virtuoso Layout Suite | Cadence Virtuoso Spectre Circuit Simulator | Cisco IOS | نرم‌افزار چیدمان نیمه‌هادی اکسید فلزی مکمل CMOS | نرم‌افزار تشخیص کامپیوتر | نرم‌افزار شبیه‌سازی کامپیوتر | Dassault Systemes CATIA | سیستم‌های جمع‌آوری داده | نرم‌افزار پایگاه داده | نرم‌افزار درج طراحی برای تست‌پذیری DFT | نرم‌افزار تحلیل تبدیل فوریه گسسته DFT | Eko | نرم‌افزار اتوماسیون طراحی الکترونیکی EDA | نرم‌افزار تحلیل خرابی | نرم‌افزار تحلیل تبدیل فوریه سریع FFT | نرم‌افزار طراحی آرایه گیت برنامه‌پذیر میدانی FPGA | نرم‌افزار سنتز منطق آرایه گیت برنامه‌پذیر میدانی FPGA | Freescale CodeWarrior Tools | Git | زبان توصیف و تأیید سخت‌افزار | زبان توصیف سخت‌افزار HDL | نرم‌افزار شبیه‌سازی مدار مجتمع | نرم‌افزار موتور جستجوی اینترنت | Linux | نرم‌افزار سنتز منطق | LogicVision icBIST | M-Sim | نرم‌افزار MAGIC | Magellan Firmware | Magma Design Automation Blast Create | Magma Design Automation Blast FPGA | MathWorks Simulink | MathWorks Simulink DSP Blockset | MathWorks Simulink Fixed-Point Blockset | Mathsoft Mathcad | Mentor Graphics BSDArchitect | Mentor Graphics Calibre | Mentor Graphics LeonardoSpectrum | Mentor Graphics Precision RTL | Mentor Graphics Xpedition xDX Designer | نرم‌افزار شبیه‌سازی ریزمعماری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual C# .NET | نرم‌افزار شبیه‌سازی مونت کارلو | National Instruments LabVIEW | Oracle Java | PARTHENON | PCI Express PCIe | PTC Creo Parametric | Perl | نرم‌افزار مکان‌یابی و مسیریابی | Python | زبان انتقال ثبات RTL | SAS | نرم‌افزار SKILL FMEA | ویرایشگرهای شماتیک | Shell script | برنامه شبیه‌سازی با تأکید بر مدار مجتمع SPICE | SoftICE | نرم‌افزار نمودار حالت | زبان پرس‌وجوی ساختاریافته SQL | Synopsys Design Compiler | Synopsys HSIM | Synopsys HSPICE | Synopsys Hercules | Synopsys TetraMax ATPG | Synplicity Synplify | SystemVerilog | The MathWorks MATLAB | The MathWorks Real-Time Workshop | The MathWorks Signal Processing Toolbox | The MathWorks Symbolic Math Toolbox | The MathWorks Wavelet Toolbox | The Mathworks Control System Toolbox | The Mathworks Data Acquisition Toolbox | The Mathworks Embedded Coder | نرم‌افزار تحلیل زمان‌بندی | زبان دستور ابزار Tcl | UNIX | نرم‌افزار تأیید | Verilog | نرم‌افزار شبیه‌سازی زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHDL | زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHDL | نرم‌افزار مرورگر وب | دیباگرهای هسته ویندوز | Xilinx ISE Foundation | Xilinx ModelSim | Xilinx Synthesis Technology XST</t>
+          <t>ASSET JTAG ScanWorks | Apache Subversion SVN | نرم‌افزار سنتز منطق مدار مجتمع با کاربرد خاص ASIC | Autodesk AutoCAD | نرم‌افزار تولید برنامه تست خودکار ATPG | نرم‌افزار نمودار بلوکی | زبان توصیف اسکن مرزی BSDL | نرم‌افزار درج اسکن مرزی | نرم‌افزار دیباگ خودآزمایی داخلی BIST | C | C++ | Cadence Allegro PCB Designer | Cadence Concept | Cadence Dracula | Cadence Encounter RTL Compiler | Cadence Opus | نرم‌افزار Cadence OrCAD | Cadence PSpice | Cadence Schematic Composer | Cadence Virtuoso Layout Suite | Cadence Virtuoso Spectre Circuit Simulator | Cisco IOS | نرم‌افزار چیدمان نیمه‌هادی اکسید فلزی مکمل CMOS | نرم‌افزار تشخیص کامپیوتر | نرم‌افزار شبیه‌سازی کامپیوتر | Dassault Systemes CATIA | سیستم‌های جمع‌آوری داده | نرم‌افزار پایگاه داده | نرم‌افزار درج طراحی برای تست‌پذیری DFT | نرم‌افزار تحلیل تبدیل فوریه گسسته DFT | Eko | نرم‌افزار اتوماسیون طراحی الکترونیکی EDA | نرم‌افزار تحلیل خرابی | نرم‌افزار تحلیل تبدیل فوریه سریع FFT | نرم‌افزار طراحی آرایه درگاه قابل برنامه‌ریزی فیلد FPGA | نرم‌افزار سنتز منطق آرایه گیت برنامه‌پذیر میدانی FPGA | Freescale CodeWarrior Tools | Git | زبان توصیف و تأیید سخت‌افزار | زبان توصیف سخت‌افزار HDL | نرم‌افزار شبیه‌سازی مدار مجتمع | نرم‌افزار موتور جستجوی اینترنت | Linux | نرم‌افزار سنتز منطق | LogicVision icBIST | M-Sim | نرم‌افزار MAGIC | Magellan Firmware | Magma Design Automation Blast Create | Magma Design Automation Blast FPGA | MathWorks Simulink | MathWorks Simulink DSP Blockset | MathWorks Simulink Fixed-Point Blockset | Mathsoft Mathcad | Mentor Graphics BSDArchitect | Mentor Graphics Calibre | Mentor Graphics LeonardoSpectrum | Mentor Graphics Precision RTL | Mentor Graphics Xpedition xDX Designer | نرم‌افزار شبیه‌سازی ریزمعماری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual C# .NET | نرم‌افزار شبیه‌سازی مونت کارلو | National Instruments LabVIEW | Oracle Java | PARTHENON | PCI Express PCIe | PTC Creo Parametric | Perl | نرم‌افزار مکان‌یابی و مسیریابی | Python | زبان انتقال ثبات RTL | SAS | نرم‌افزار SKILL FMEA | ویرایشگرهای شماتیک | Shell script | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | SoftICE | نرم‌افزار نمودار حالت | زبان پرس‌وجوی ساختاریافته SQL | Synopsys Design Compiler | Synopsys HSIM | Synopsys HSPICE | Synopsys Hercules | Synopsys TetraMax ATPG | Synplicity Synplify | SystemVerilog | The MathWorks MATLAB | The MathWorks Real-Time Workshop | The MathWorks Signal Processing Toolbox | The MathWorks Symbolic Math Toolbox | The MathWorks Wavelet Toolbox | The Mathworks Control System Toolbox | The Mathworks Data Acquisition Toolbox | The Mathworks Embedded Coder | نرم‌افزار تحلیل زمان‌بندی | زبان دستور ابزار Tcl | UNIX | نرم‌افزار تأیید | Verilog | نرم‌افزار شبیه‌سازی زبان توصیف سخت‌افزار VHSIC با سرعت بسیار بالا VHDL | زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHSIC VHDL | نرم‌افزار مرورگر وب | دیباگرهای هسته ویندوز | Xilinx ISE Foundation | Xilinx ModelSim | Xilinx Synthesis Technology XST</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نوشتن | صحبت کردن | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مهندسی و فناوری | ریاضیات | طراحی | زبان انگلیسی | فیزیک | مخابرات</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | طراحی | زبان انگلیسی | فیزیک | مخابرات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | استدلال استقرایی | نظم‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | بیان نوشتاری | دید نزدیک | انعطاف‌پذیری دسته‌بندی | اصالت | وضوح گفتار | تجسم | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | توانایی کار با اعداد | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | اصالت | وضوح گفتار | تجسم | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | بحث‌های حضوری با افراد و درون تیم‌ها | فضای بسته، با محیط کنترل‌شده | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | سطح رقابت | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | سطح رقابت | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Calibration Technologists and Technicians | Computer Numerically Controlled Tool Programmers | Computer Systems Analysts | Computer Systems Engineers/Architects | Electrical Engineers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Drafters | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electro-Mechanical and Mechatronics Technologists and Technicians | Electronics Engineers, Except Computer | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Mechatronics Engineers | Microsystems Engineers | Photonics Engineers | Radio Frequency Identification Device Specialists | Robotics Engineers | Robotics Technicians | Software Developers | Software Quality Assurance Analysts and Testers</t>
+          <t>تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان فوتونیک | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0016_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0016_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | شنیدن فعال | یادگیری فعال | استراتژی‌های یادگیری | نظارت</t>
+          <t>ریاضیات | درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | مهندسی و فناوری | جغرافیا | رایانه و الکترونیک | طراحی | خدمات مشتریان و خدمات فردی | ساختمان و ساخت‌وساز | مدیریت و امور اداری | زبان انگلیسی | حقوق و امور دولتی | آموزش و تدریس | امور دفتری و اداری | امور اداری و منابع انسانی</t>
+          <t>ریاضیات | مهندسی و فناوری | جغرافیا | رایانه و الکترونیک | طراحی | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مدیریت و اداره | زبان انگلیسی | قانون و دولت | آموزش و پرورش | اداری | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | استدلال ریاضی | دید نزدیک | بیان کتبی | استدلال استقرایی | محاسبات عددی | درک شفاهی | بیان شفاهی | دید دور | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | تجسم فضایی | جهت‌یابی فضایی | سرعت ادراک | انعطاف‌پذیری ساختارشکنی | توجه انتخابی | سرعت ساختارشکنی | روانی کلام و ایده | ادراک عمق | دقت کنترل حرکتی | چابکی انگشتان | ثبات دست و بازو</t>
+          <t>درک کتبی | استدلال قیاسی | استدلال ریاضی | بینایی نزدیک | بیان کتبی | استدلال استقرایی | توانایی عددی | درک شفاهی | بیان شفاهی | بینایی دور | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تجسم | جهت‌گیری فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت بستار | روانی ایده‌ها | درک عمق | دقت کنترل | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ارزیابان و کارشناسان قیمت‌گذاری املاک | معماران، به‌جز معماری منظر و معماری دریایی | نقشه‌کش‌های معماری و عمران | کارتوگراف‌ها و فتوگرامتریست‌ها | تکنسین‌ها و کاردان‌های مهندسی عمران | مهندسان عمران | کارشناسان حفاظت از منابع طبیعی | مدیران پروژه‌های عمرانی و ساختمانی | بازرسان فنی ساختمان و سازه | کارشناسان متره، برآورد و آنالیز بها | تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | مهندسان نقشه‌برداری ژئودزی | تکنسین‌های زمین‌شناسی، به‌جز تکنسین‌های هیدرولوژی | زمین‌شناسان و دانشمندان علوم زمین، به‌جز هیدرولوژیست‌ها و جغرافیدانان | بازرسان و ممیزان اموال دولتی | هیدرولوژیست‌ها (متخصصان منابع آب) | مهندسان معماری منظر | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | کاردان‌ها و تکنسین‌های نقشه‌برداری و نقشه‌نگاری | بازرسان فنی سیستم‌های حمل‌ونقل</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | کارشناسان نقشه‌نگاری و فتوگرامتری | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | کارشناسان برآورد هزینه و مترورها | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | مهندسان نقشه‌برداری ژئودزی | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | بازرسان و ممیزان اموال دولتی | آب‌شناسان و هیدرولوژیست‌ها | مهندسان معمار منظر | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم پایه | استراتژی‌های یادگیری</t>
+          <t>ریاضیات | درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ریاضیات | مهندسی و فناوری | جغرافیا | رایانه و الکترونیک | زبان انگلیسی | فیزیک | آموزش و تدریس | طراحی | خدمات مشتریان و خدمات فردی</t>
+          <t>ریاضیات | مهندسی و فناوری | جغرافیا | رایانه و الکترونیک | زبان انگلیسی | فیزیک | آموزش و پرورش | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال ریاضی | انعطاف‌پذیری ساختارشکنی | مرتب‌سازی اطلاعات | محاسبات عددی | دید نزدیک | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | حساسیت به مسئله | تجسم فضایی | وضوح گفتار | روانی کلام و ایده | تشخیص گفتار | دید دور | توجه انتخابی | سرعت ادراک | سرعت ساختارشکنی | حافظه و یادسپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال ریاضی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | توانایی عددی | بینایی نزدیک | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | تجسم | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | بینایی دور | توجه انتخابی | سرعت ادراکی | سرعت بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>نقشه‌کش‌های معماری و عمران | دانشمندان علوم جوی و فضا | کاردان‌ها و تکنسین‌های کالیبراسیون و ابزار دقیق | کارتوگراف‌ها و فتوگرامتریست‌ها | تکنسین‌ها و کاردان‌های مهندسی عمران | مهندسان عمران | دانشمندان علم داده | تکنسین‌ها و کاردان‌های مهندسی برق و الکترونیک | جغرافیدانان | کاردان‌ها و تکنسین‌های سامانه‌های اطلاعات جغرافیایی GIS | تکنسین‌های زمین‌شناسی، به‌جز تکنسین‌های هیدرولوژی | زمین‌شناسان و دانشمندان علوم زمین، به‌جز هیدرولوژیست‌ها و جغرافیدانان | تکنسین‌های هیدرولوژی (آب‌شناسی) | هیدرولوژیست‌ها (متخصصان منابع آب) | کارشناسان و متخصصان سنجش از دور | تکنسین‌های سنجش از دور | دستیاران و کمک‌کارشناسان آمار | کاردان‌ها و تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان نقشه‌برداری | تکنسین‌های ترافیک و حمل‌ونقل</t>
+          <t>نقشه‌کشان معماری و عمران | دانشمندان و کارشناسان علوم جوی و فضا | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان نقشه‌نگاری و فتوگرامتری | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | دانشمندان داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | جغرافیدانان | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | دستیاران و تکنسین‌های آمار | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان نقشه‌برداری | تکنسین‌های ترافیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم پایه | درک مطلب | نگارش | سخن گفتن | ریاضیات | شنیدن فعال | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | علوم | درک مطلب | نگارش | سخن گفتن | ریاضیات | گوش دادن فعال | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان کتبی | استدلال ریاضی | درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | روانی کلام و ایده | انعطاف‌پذیری در طبقه‌بندی | تشخیص گفتار | محاسبات عددی | ابتکار و اصالت | تجسم فضایی | دید دور | انعطاف‌پذیری ساختارشکنی | توجه انتخابی | سرعت ادراک | تشخیص رنگ‌ها</t>
+          <t>درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال ریاضی | درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توانایی عددی | اصالت | تجسم | بینایی دور | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های فنی و عملیات مهندسی هوافضا | مکانیک‌ها و تعمیرکاران هواپیما | مونتاژکاران سازه، سطوح و سامانه‌های هواپیما | تکنسین‌های مهندسی خودرو | مهندسان خودرو | تکنسین‌های اویونیک و اویونیک پرواز | کاردان‌ها و تکنسین‌های کالیبراسیون و ابزار دقیق | مهندسان برق | تکنسین‌ها و کاردان‌های مهندسی برق و الکترونیک | تکنسین‌ها و کاردان‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | تکنسین‌ها و کاردان‌های مهندسی صنایع | مهندسان صنایع | مهندسان ساخت و تولید | مهندسان دریایی و معماران کشتی | تکنسین‌ها و کاردان‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | مهندسان خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان دریایی و معماران کشتی | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | ریاضیات | علوم پایه | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | علوم | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | رایانه و الکترونیک | طراحی | فیزیک | ریاضیات | زیست‌شناسی | مکانیک | زبان انگلیسی | تولیدات کشاورزی و دامی | شیمی | تولید و فرآوری | ساختمان و ساخت‌وساز | جغرافیا | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | آموزش و تدریس</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | طراحی | فیزیک | ریاضیات | زیست‌شناسی | مکانیک | زبان انگلیسی | تولید مواد غذایی | شیمی | تولید و فرآوری | ساختمان و ساخت‌وساز | جغرافیا | مدیریت و اداره | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | تجسم فضایی | دید نزدیک | وضوح گفتار | روانی کلام و ایده | تشخیص گفتار | استدلال ریاضی | ابتکار و اصالت | محاسبات عددی | دید دور | توجه انتخابی | انعطاف‌پذیری ساختارشکنی</t>
+          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تجسم | بینایی نزدیک | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | استدلال ریاضی | اصالت | توانایی عددی | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>استادان علوم کشاورزی دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌ها و کاردان‌های کشاورزی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری بیودیزل و سوخت‌های زیستی | مهندسان عمران | کارشناسان حفاظت از منابع طبیعی | کاردان‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | دانشمندان و کارشناسان محیط زیست، شامل بهداشت محیط | تعمیرکاران و مکانیک‌های ماشین‌آلات و ادوات کشاورزی | کشاورزان، دامداران و مدیران مزارع و کشت و صنعت‌ها | تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | مدیران تولید انرژی زمین‌گرمایی | اکولوژیست‌های صنعتی | تکنسین‌ها و کاردان‌های مهندسی صنایع | مهندسان صنایع | تکنسین‌های کشاورزی دقیق | کارشناسان علوم خاک و گیاه‌پزشکی | متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب</t>
+          <t>استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کشاورزی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | مدیران امور کشاورزی، دامپروری و شیلات | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | مدیران تولید انرژی زمین‌گرمایی | بوم‌شناسان صنعتی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | تکنسین‌های کشاورزی دقیق | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان و متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | علوم پایه | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | علوم | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | فیزیک | طراحی | زیست‌شناسی | زبان انگلیسی | پزشکی و دندان‌پزشکی | آموزش و تدریس | شیمی | مدیریت و امور اداری</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | فیزیک | طراحی | زیست‌شناسی | زبان انگلیسی | پزشکی و دندان‌پزشکی | آموزش و پرورش | شیمی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | مرتب‌سازی اطلاعات | روانی کلام و ایده | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | تشخیص گفتار | تجسم فضایی | انعطاف‌پذیری ساختارشکنی | محاسبات عددی | وضوح گفتار | توجه انتخابی | سرعت ادراک</t>
+          <t>استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | اصالت | تشخیص گفتار | تجسم | انعطاف‌پذیری بستار | توانایی عددی | وضوح گفتار | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدانان | دانشمندان و متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | تکنسین‌ها و کاردان‌های زیست‌شناسی | کاردان‌ها و تکنسین‌های کالیبراسیون و ابزار دقیق | مهندسان شیمی | شیمیدانان | مدیران داده‌های بالینی و کارآزمایی بالینی | دانشمندان علم داده | متخصصان ژنتیک | تکنسین‌ها و کاردان‌های مهندسی صنایع | دانشمندان علم مواد | تکنسین‌ها و کاردان‌های مهندسی مکانیک | تعمیرکاران و کارشناسان تعمیر تجهیزات پزشکی | تکنسین‌ها و کارشناسان آزمایشگاه‌های تشخیص طبی و بالینی | میکروبیولوژیست‌ها | متخصصان زیست‌شناسی سلولی و مولکولی | مهندسان نانوسیستم‌ها | تکنسین‌ها و کاردان‌های مهندسی نانوتکنولوژی | مدیران علوم طبیعی و پایه</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | تکنسین‌های علوم زیستی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان شیمی | شیمی‌دانان | مدیران داده‌های بالینی | دانشمندان داده | متخصصان ژنتیک | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | تعمیرکاران تجهیزات پزشکی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مدیران علوم طبیعی و پایه‌ای</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>علوم پایه | تفکر انتقادی | درک مطلب | یادگیری فعال | ریاضیات | سخن گفتن | شنیدن فعال | نگارش | نظارت</t>
+          <t>علوم | تفکر انتقادی | درک مطلب | یادگیری فعال | ریاضیات | سخن گفتن | گوش دادن فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | انعطاف‌پذیری در طبقه‌بندی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال ریاضی | دید نزدیک | محاسبات عددی | ابتکار و اصالت | روانی کلام و ایده | انعطاف‌پذیری ساختارشکنی | بیان کتبی | تجسم فضایی | سرعت ادراک | وضوح گفتار | تشخیص گفتار | دید دور | توجه انتخابی | سرعت ساختارشکنی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | بینایی نزدیک | توانایی عددی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار | بیان کتبی | تجسم | سرعت ادراکی | وضوح گفتار | تشخیص گفتار | بینایی دور | توجه انتخابی | سرعت بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | مدیران توسعه محصول و فناوری بیودیزل و سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده (بیومس) | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای پالایشگاه و مجتمع‌های پتروشیمی | تکنسین‌ها و کاردان‌های شیمی | شیمیدانان | مهندسان پیل سوختی | تکنسین‌ها و کاردان‌های مهندسی صنایع | مهندسان صنایع | مهندسان ساخت و تولید | مهندسان متالورژی و مواد | دانشمندان علم مواد | تکنسین‌ها و کاردان‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان نانوسیستم‌ها | تکنسین‌ها و کاردان‌های مهندسی نانوتکنولوژی | مهندسان هسته‌ای | مهندسان نفت</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | تکنسین‌های شیمی | شیمی‌دانان | مهندسان پیل سوختی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان متالورژی و مواد | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مهندسان هسته‌ای | مهندسان نفت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | ریاضیات | درک مطلب | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | ریاضیات | درک مطلب | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | ساختمان و ساخت‌وساز | ریاضیات | زبان انگلیسی | فیزیک | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | حقوق و امور دولتی | ایمنی و امنیت عمومی | رایانه و الکترونیک | حمل‌ونقل</t>
+          <t>طراحی | مهندسی و فناوری | ساختمان و ساخت‌وساز | ریاضیات | زبان انگلیسی | فیزیک | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | ایمنی و امنیت عمومی | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | محاسبات عددی | تجسم فضایی | روانی کلام و ایده | دید نزدیک | دید دور | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری ساختارشکنی | سرعت ادراک | ابتکار و اصالت | توجه انتخابی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | تجسم | روانی ایده‌ها | بینایی نزدیک | بینایی دور | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | سرعت ادراکی | اصالت | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>معماران، به‌جز معماری منظر و معماری دریایی | نقشه‌کش‌های معماری و عمران | مدیران معماری و مهندسی | متخصصان و مدیران احیا و بازآفرینی اراضی صنعتی فرسوده | تکنسین‌ها و کاردان‌های مهندسی عمران | مدیران پروژه‌های عمرانی و ساختمانی | بازرسان فنی ساختمان و سازه | مهندسان برق | مهندسان محیط زیست | مدیران امور تاسیسات و نگهداری ابنیه | سرپرستان و استادکاران کارگاه‌های ساختمانی و استخراج | مهندسان صنایع | کارشناسان و تعمیرکاران فنی عمومی | مهندسان دریایی و معماران کشتی | تکنسین‌ها و کاردان‌های مهندسی مکانیک | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | مدیران اجرایی نصب تجهیزات انرژی خورشیدی | مهندسان راه و ترابری و حمل‌ونقل | مهندسان آب و فاضلاب | مهندسان انرژی بادی</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | مدیران فنی و مهندسی و معماری | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | کارشناسان و تکنسین‌های مهندسی عمران | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | مهندسان برق | مهندسان محیط‌زیست | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | مهندسان صنایع | کارگران عمومی تعمیرات و نگهداری تاسیسات | مهندسان دریایی و معماران کشتی | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | مدیران اجرای پروژه‌های انرژی خورشیدی | مهندسان حمل‌ونقل و ترافیک | مهندسان آب و فاضلاب | مهندسان انرژی باد</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | ریاضیات | شنیدن فعال | نظارت | یادگیری فعال | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | ریاضیات | گوش دادن فعال | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | حمل‌ونقل | ساختمان و ساخت‌وساز | ریاضیات | زبان انگلیسی | فیزیک | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | حقوق و امور دولتی | ایمنی و امنیت عمومی | آموزش و تدریس</t>
+          <t>مهندسی و فناوری | طراحی | حمل و نقل | ساختمان و ساخت‌وساز | ریاضیات | زبان انگلیسی | فیزیک | مدیریت و اداره | خدمات مشتری و شخصی | رایانه و الکترونیک | قانون و دولت | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | انعطاف‌پذیری در طبقه‌بندی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال ریاضی | محاسبات عددی | مرتب‌سازی اطلاعات | تجسم فضایی | دید نزدیک | تشخیص گفتار | روانی کلام و ایده | وضوح گفتار | دید دور | ابتکار و اصالت | انعطاف‌پذیری ساختارشکنی | توجه انتخابی | سرعت ادراک</t>
+          <t>استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال ریاضی | توانایی عددی | ترتیب‌دهی اطلاعات | تجسم | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | وضوح گفتار | بینایی دور | اصالت | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان هوافضا | نقشه‌کش‌های معماری و عمران | مدیران معماری و مهندسی | مهندسان خودرو | متخصصان و مدیران احیا و بازآفرینی اراضی صنعتی فرسوده | تکنسین‌ها و کاردان‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های عمرانی و ساختمانی | بازرسان فنی ساختمان و سازه | مهندسان محیط زیست | کارگران نگهداری و مرمت بزرگراه‌ها و راه‌ها | مهندسان صنایع | مهندسان لجستیک و زنجیره تامین | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | کارشناسان مدیریت پروژه | مدیران اجرایی نصب تجهیزات انرژی خورشیدی | تکنسین‌های ترافیک و حمل‌ونقل | کارشناسان برنامه‌ریزی حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع | مهندسان آب و فاضلاب</t>
+          <t>مهندسان هوافضا | نقشه‌کشان معماری و عمران | مدیران فنی و مهندسی و معماری | مهندسان خودرو | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | مهندسان محیط‌زیست | کارگران راهداری و نگهداری جاده‌ها | مهندسان صنایع | مهندسان لجستیک و زنجیره تأمین | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | کارشناسان مدیریت پروژه | مدیران اجرای پروژه‌های انرژی خورشیدی | تکنسین‌های ترافیک | برنامه‌ریزان سیستم‌های حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نگارش | درک مطلب | شنیدن فعال | ریاضیات | سخن گفتن | نظارت | علوم پایه | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | نگارش | درک مطلب | گوش دادن فعال | ریاضیات | سخن گفتن | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | زبان انگلیسی | ریاضیات | ساختمان و ساخت‌وساز | مدیریت و امور اداری | مکانیک | فیزیک | شیمی | خدمات مشتریان و خدمات فردی | حقوق و امور دولتی | زیست‌شناسی | بازاریابی و فروش | رایانه و الکترونیک | اقتصاد و حسابداری</t>
+          <t>مهندسی و فناوری | طراحی | زبان انگلیسی | ریاضیات | ساختمان و ساخت‌وساز | مدیریت و اداره | مکانیک | فیزیک | شیمی | خدمات مشتری و شخصی | قانون و دولت | زیست‌شناسی | فروش و بازاریابی | رایانه و الکترونیک | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | روانی کلام و ایده | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | محاسبات عددی | تجسم فضایی | دید نزدیک | ابتکار و اصالت | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری ساختارشکنی | دید دور | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | تجسم | بینایی نزدیک | اصالت | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | بینایی دور | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متخصصان و مدیران احیا و بازآفرینی اراضی صنعتی فرسوده | مهندسان شیمی | مهندسان عمران | کارشناسان حفاظت از منابع طبیعی | مهندسان انرژی، به‌جز باد و خورشید | کاردان‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | کارشناسان برنامه‌ریزی احیای محیط زیست | تکنسین‌های علوم زیست‌محیطی و بهداشت محیط | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران بهره‌برداری نیروگاه‌های برق‌آبی | تکنسین‌های هیدرولوژی (آب‌شناسی) | هیدرولوژیست‌ها (متخصصان منابع آب) | اکولوژیست‌های صنعتی | مهندسان نفت | مهندسان راه و ترابری و حمل‌ونقل | متخصصان مدیریت منابع آب | اپراتورها و کارشناسان بهره‌برداری تصفیه‌خانه‌های آب و فاضلاب | مهندسان انرژی بادی</t>
+          <t>مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مهندسان شیمی | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | مهندسان انرژی، به‌جز بادی و خورشیدی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مهندسان نفت | مهندسان حمل‌ونقل و ترافیک | کارشناسان و متخصصان مدیریت منابع آب | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | مهندسان انرژی باد</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | طراحی | زبان انگلیسی | فیزیک | مخابرات و ارتباطات</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | طراحی | زبان انگلیسی | فیزیک | مخابرات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | وضوح گفتار | تجسم فضایی | تشخیص گفتار | روانی کلام و ایده | انعطاف‌پذیری ساختارشکنی | محاسبات عددی | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | اصالت | وضوح گفتار | تجسم | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های کالیبراسیون و ابزار دقیق | برنامه‌نویسان ماشین‌های کنترل عددی رایانه‌ای CNC | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سیستم‌های کامپیوتری | مهندسان برق | تکنسین‌ها و کاردان‌های مهندسی برق و الکترونیک | نقشه‌کش‌های برق و الکترونیک | تعمیرکاران تجهیزات الکترونیکی و تجاری صنعتی | تکنسین‌ها و کاردان‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | تکنسین‌ها و کاردان‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | مهندسان فوتونیک و اپتیک | کارشناسان تجهیزات شناسایی امواج رادیویی RFID | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و کارشناسان تست و تضمین کیفیت نرم‌افزار</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان فوتونیک | متخصصان سامانه‌های شناسایی با امواج رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
